--- a/docs/sheet/nichihara-update.xlsx
+++ b/docs/sheet/nichihara-update.xlsx
@@ -949,7 +949,7 @@
       <formula1>"公開する,下書き"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"お知らせ,休館・営業,道路・アクセス,メディア"</formula1>
+      <formula1>"お知らせ,イベント,天文情報,活動報告,休館・営業,道路・アクセス,メディア"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"○"</formula1>
